--- a/4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl/test-results/3x1_vs_abbyy_errors_artifacts.xlsx
+++ b/4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl/test-results/3x1_vs_abbyy_errors_artifacts.xlsx
@@ -788,7 +788,7 @@
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap issue count</t>
+          <t>Possible duplicate lines issue count</t>
         </is>
       </c>
       <c r="B9" s="1" t="inlineStr">
@@ -1334,12 +1334,12 @@
       </c>
       <c r="E22" s="1" t="inlineStr">
         <is>
-          <t>paddle duplicate/tile overlap</t>
+          <t>paddle Possible duplicate lines</t>
         </is>
       </c>
       <c r="F22" s="1" t="inlineStr">
         <is>
-          <t>abbyy duplicate/tile overlap</t>
+          <t>abbyy Possible duplicate lines</t>
         </is>
       </c>
       <c r="G22" s="1" t="inlineStr">
@@ -2480,12 +2480,12 @@
       </c>
       <c r="G32" s="1" t="inlineStr">
         <is>
-          <t>paddle duplicate/tile overlap</t>
+          <t>paddle Possible duplicate lines</t>
         </is>
       </c>
       <c r="H32" s="1" t="inlineStr">
         <is>
-          <t>abbyy duplicate/tile overlap</t>
+          <t>abbyy Possible duplicate lines</t>
         </is>
       </c>
       <c r="I32" s="1" t="inlineStr">
